--- a/artfynd/A 56788-2023 artfynd.xlsx
+++ b/artfynd/A 56788-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121416640</v>
+        <v>121416560</v>
       </c>
       <c r="B2" t="n">
-        <v>56555</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näveråsen, Näveråsen, Dlr</t>
+          <t>Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485045</v>
+        <v>485067</v>
       </c>
       <c r="R2" t="n">
-        <v>6850175</v>
+        <v>6850123</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121414507</v>
+        <v>121413886</v>
       </c>
       <c r="B3" t="n">
         <v>98081</v>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484938</v>
+        <v>484910</v>
       </c>
       <c r="R3" t="n">
-        <v>6850191</v>
+        <v>6850188</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121413976</v>
+        <v>121414555</v>
       </c>
       <c r="B4" t="n">
         <v>98081</v>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484940</v>
+        <v>484975</v>
       </c>
       <c r="R4" t="n">
-        <v>6850189</v>
+        <v>6850186</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121413581</v>
+        <v>121414642</v>
       </c>
       <c r="B5" t="n">
         <v>98081</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484920</v>
+        <v>484941</v>
       </c>
       <c r="R5" t="n">
-        <v>6850189</v>
+        <v>6850185</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121414725</v>
+        <v>121414636</v>
       </c>
       <c r="B6" t="n">
         <v>98081</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484937</v>
+        <v>484958</v>
       </c>
       <c r="R6" t="n">
-        <v>6850172</v>
+        <v>6850185</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1178,19 +1178,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121413920</v>
+        <v>121414725</v>
       </c>
       <c r="B7" t="n">
         <v>98081</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484950</v>
+        <v>484937</v>
       </c>
       <c r="R7" t="n">
-        <v>6850202</v>
+        <v>6850172</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1280,19 +1280,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121413886</v>
+        <v>121413976</v>
       </c>
       <c r="B8" t="n">
         <v>98081</v>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484910</v>
+        <v>484940</v>
       </c>
       <c r="R8" t="n">
-        <v>6850188</v>
+        <v>6850189</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,19 +1382,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121414555</v>
+        <v>121413957</v>
       </c>
       <c r="B9" t="n">
         <v>98081</v>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484975</v>
+        <v>484948</v>
       </c>
       <c r="R9" t="n">
-        <v>6850186</v>
+        <v>6850191</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1470,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121413957</v>
+        <v>121413920</v>
       </c>
       <c r="B10" t="n">
         <v>98081</v>
@@ -1541,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484948</v>
+        <v>484950</v>
       </c>
       <c r="R10" t="n">
-        <v>6850191</v>
+        <v>6850202</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121413972</v>
+        <v>121413581</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484943</v>
+        <v>484920</v>
       </c>
       <c r="R11" t="n">
-        <v>6850255</v>
+        <v>6850189</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121415337</v>
+        <v>121416640</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>56555</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,41 +1712,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485020</v>
+        <v>485045</v>
       </c>
       <c r="R12" t="n">
-        <v>6850196</v>
+        <v>6850175</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121414642</v>
+        <v>121413972</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484941</v>
+        <v>484943</v>
       </c>
       <c r="R13" t="n">
-        <v>6850185</v>
+        <v>6850255</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121414636</v>
+        <v>121414593</v>
       </c>
       <c r="B14" t="n">
         <v>98081</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484958</v>
+        <v>484949</v>
       </c>
       <c r="R14" t="n">
-        <v>6850185</v>
+        <v>6850202</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1999,19 +1999,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121416254</v>
+        <v>121415337</v>
       </c>
       <c r="B15" t="n">
         <v>98081</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485054</v>
+        <v>485020</v>
       </c>
       <c r="R15" t="n">
-        <v>6850120</v>
+        <v>6850196</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2101,19 +2101,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121414593</v>
+        <v>121414507</v>
       </c>
       <c r="B16" t="n">
         <v>98081</v>
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484949</v>
+        <v>484938</v>
       </c>
       <c r="R16" t="n">
-        <v>6850202</v>
+        <v>6850191</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121416560</v>
+        <v>121416254</v>
       </c>
       <c r="B17" t="n">
         <v>98081</v>
@@ -2251,14 +2251,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näveråsen, Dlr</t>
+          <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485067</v>
+        <v>485054</v>
       </c>
       <c r="R17" t="n">
-        <v>6850123</v>
+        <v>6850120</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2305,12 +2305,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 56788-2023 artfynd.xlsx
+++ b/artfynd/A 56788-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121416560</v>
+        <v>121414636</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näveråsen, Dlr</t>
+          <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485067</v>
+        <v>484958</v>
       </c>
       <c r="R2" t="n">
-        <v>6850123</v>
+        <v>6850185</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121413886</v>
+        <v>121413920</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484910</v>
+        <v>484950</v>
       </c>
       <c r="R3" t="n">
-        <v>6850188</v>
+        <v>6850202</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121414555</v>
+        <v>121413886</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484975</v>
+        <v>484910</v>
       </c>
       <c r="R4" t="n">
-        <v>6850186</v>
+        <v>6850188</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -957,11 +957,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -974,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121414642</v>
+        <v>121414507</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484941</v>
+        <v>484938</v>
       </c>
       <c r="R5" t="n">
-        <v>6850185</v>
+        <v>6850191</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121414636</v>
+        <v>121413976</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484958</v>
+        <v>484940</v>
       </c>
       <c r="R6" t="n">
-        <v>6850185</v>
+        <v>6850189</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,7 +1188,7 @@
         <v>121414725</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121413976</v>
+        <v>121416640</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>56555</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,41 +1299,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484940</v>
+        <v>485045</v>
       </c>
       <c r="R8" t="n">
-        <v>6850189</v>
+        <v>6850175</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121413957</v>
+        <v>121413581</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484948</v>
+        <v>484920</v>
       </c>
       <c r="R9" t="n">
-        <v>6850191</v>
+        <v>6850189</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1484,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121413920</v>
+        <v>121413972</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484950</v>
+        <v>484943</v>
       </c>
       <c r="R10" t="n">
-        <v>6850202</v>
+        <v>6850255</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1586,22 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121413581</v>
+        <v>121416254</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484920</v>
+        <v>485054</v>
       </c>
       <c r="R11" t="n">
-        <v>6850189</v>
+        <v>6850120</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121416640</v>
+        <v>121416560</v>
       </c>
       <c r="B12" t="n">
-        <v>56555</v>
+        <v>98094</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,46 +1712,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Näveråsen, Näveråsen, Dlr</t>
+          <t>Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485045</v>
+        <v>485067</v>
       </c>
       <c r="R12" t="n">
-        <v>6850175</v>
+        <v>6850123</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,22 +1790,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121413972</v>
+        <v>121414593</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484943</v>
+        <v>484949</v>
       </c>
       <c r="R13" t="n">
-        <v>6850255</v>
+        <v>6850202</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1909,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121414593</v>
+        <v>121414555</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484949</v>
+        <v>484975</v>
       </c>
       <c r="R14" t="n">
-        <v>6850202</v>
+        <v>6850186</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1987,6 +1982,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -1999,22 +1999,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121415337</v>
+        <v>121414642</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485020</v>
+        <v>484941</v>
       </c>
       <c r="R15" t="n">
-        <v>6850196</v>
+        <v>6850185</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2101,22 +2101,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121414507</v>
+        <v>121413957</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484938</v>
+        <v>484948</v>
       </c>
       <c r="R16" t="n">
         <v>6850191</v>
@@ -2203,22 +2203,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121416254</v>
+        <v>121414073</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485054</v>
+        <v>484929</v>
       </c>
       <c r="R17" t="n">
-        <v>6850120</v>
+        <v>6850187</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2305,22 +2305,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121414073</v>
+        <v>121415337</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2357,13 +2357,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484929</v>
+        <v>485020</v>
       </c>
       <c r="R18" t="n">
-        <v>6850187</v>
+        <v>6850196</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 56788-2023 artfynd.xlsx
+++ b/artfynd/A 56788-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121414636</v>
+        <v>121414073</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484958</v>
+        <v>484929</v>
       </c>
       <c r="R2" t="n">
-        <v>6850185</v>
+        <v>6850187</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121413920</v>
+        <v>121413957</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484950</v>
+        <v>484948</v>
       </c>
       <c r="R3" t="n">
-        <v>6850202</v>
+        <v>6850191</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121413886</v>
+        <v>121413972</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484910</v>
+        <v>484943</v>
       </c>
       <c r="R4" t="n">
-        <v>6850188</v>
+        <v>6850255</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121414507</v>
+        <v>121415337</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484938</v>
+        <v>485020</v>
       </c>
       <c r="R5" t="n">
-        <v>6850191</v>
+        <v>6850196</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121413976</v>
+        <v>121416560</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,17 +1119,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Näveråsen, Näveråsen, Dlr</t>
+          <t>Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484940</v>
+        <v>485067</v>
       </c>
       <c r="R6" t="n">
-        <v>6850189</v>
+        <v>6850123</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121414725</v>
+        <v>121414507</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484937</v>
+        <v>484938</v>
       </c>
       <c r="R7" t="n">
-        <v>6850172</v>
+        <v>6850191</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121416640</v>
+        <v>121414555</v>
       </c>
       <c r="B8" t="n">
-        <v>56555</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,46 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485045</v>
+        <v>484975</v>
       </c>
       <c r="R8" t="n">
-        <v>6850175</v>
+        <v>6850186</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121413581</v>
+        <v>121416254</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484920</v>
+        <v>485054</v>
       </c>
       <c r="R9" t="n">
-        <v>6850189</v>
+        <v>6850120</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121413972</v>
+        <v>121414593</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484943</v>
+        <v>484949</v>
       </c>
       <c r="R10" t="n">
-        <v>6850255</v>
+        <v>6850202</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121416254</v>
+        <v>121414642</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485054</v>
+        <v>484941</v>
       </c>
       <c r="R11" t="n">
-        <v>6850120</v>
+        <v>6850185</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121416560</v>
+        <v>121414636</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,14 +1736,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Näveråsen, Dlr</t>
+          <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485067</v>
+        <v>484958</v>
       </c>
       <c r="R12" t="n">
-        <v>6850123</v>
+        <v>6850185</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121414593</v>
+        <v>121413581</v>
       </c>
       <c r="B13" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484949</v>
+        <v>484920</v>
       </c>
       <c r="R13" t="n">
-        <v>6850202</v>
+        <v>6850189</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121414555</v>
+        <v>121413886</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484975</v>
+        <v>484910</v>
       </c>
       <c r="R14" t="n">
-        <v>6850186</v>
+        <v>6850188</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,11 +1982,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -1999,22 +1994,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121414642</v>
+        <v>121413976</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484941</v>
+        <v>484940</v>
       </c>
       <c r="R15" t="n">
-        <v>6850185</v>
+        <v>6850189</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2101,22 +2096,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121413957</v>
+        <v>121414725</v>
       </c>
       <c r="B16" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484948</v>
+        <v>484937</v>
       </c>
       <c r="R16" t="n">
-        <v>6850191</v>
+        <v>6850172</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2203,22 +2198,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121414073</v>
+        <v>121413920</v>
       </c>
       <c r="B17" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2255,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484929</v>
+        <v>484950</v>
       </c>
       <c r="R17" t="n">
-        <v>6850187</v>
+        <v>6850202</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121415337</v>
+        <v>121416640</v>
       </c>
       <c r="B18" t="n">
-        <v>98094</v>
+        <v>56555</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,41 +2324,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485020</v>
+        <v>485045</v>
       </c>
       <c r="R18" t="n">
-        <v>6850196</v>
+        <v>6850175</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2407,12 +2407,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 56788-2023 artfynd.xlsx
+++ b/artfynd/A 56788-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121414073</v>
+        <v>121413976</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484929</v>
+        <v>484940</v>
       </c>
       <c r="R2" t="n">
-        <v>6850187</v>
+        <v>6850189</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121413957</v>
+        <v>121413886</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484948</v>
+        <v>484910</v>
       </c>
       <c r="R3" t="n">
-        <v>6850191</v>
+        <v>6850188</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121413972</v>
+        <v>121413581</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484943</v>
+        <v>484920</v>
       </c>
       <c r="R4" t="n">
-        <v>6850255</v>
+        <v>6850189</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121415337</v>
+        <v>121416254</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485020</v>
+        <v>485054</v>
       </c>
       <c r="R5" t="n">
-        <v>6850196</v>
+        <v>6850120</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121416560</v>
+        <v>121413957</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,17 +1119,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Näveråsen, Dlr</t>
+          <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485067</v>
+        <v>484948</v>
       </c>
       <c r="R6" t="n">
-        <v>6850123</v>
+        <v>6850191</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121414507</v>
+        <v>121413972</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484938</v>
+        <v>484943</v>
       </c>
       <c r="R7" t="n">
-        <v>6850191</v>
+        <v>6850255</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121414555</v>
+        <v>121413920</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484975</v>
+        <v>484950</v>
       </c>
       <c r="R8" t="n">
-        <v>6850186</v>
+        <v>6850202</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1363,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121416254</v>
+        <v>121414073</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485054</v>
+        <v>484929</v>
       </c>
       <c r="R9" t="n">
-        <v>6850120</v>
+        <v>6850187</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1484,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121414593</v>
+        <v>121416640</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>56558</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,41 +1503,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484949</v>
+        <v>485045</v>
       </c>
       <c r="R10" t="n">
-        <v>6850202</v>
+        <v>6850175</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121414642</v>
+        <v>121414593</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484941</v>
+        <v>484949</v>
       </c>
       <c r="R11" t="n">
-        <v>6850185</v>
+        <v>6850202</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121414636</v>
+        <v>121414507</v>
       </c>
       <c r="B12" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484958</v>
+        <v>484938</v>
       </c>
       <c r="R12" t="n">
-        <v>6850185</v>
+        <v>6850191</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1790,22 +1790,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121413581</v>
+        <v>121414642</v>
       </c>
       <c r="B13" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484920</v>
+        <v>484941</v>
       </c>
       <c r="R13" t="n">
-        <v>6850189</v>
+        <v>6850185</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121413886</v>
+        <v>121414725</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484910</v>
+        <v>484937</v>
       </c>
       <c r="R14" t="n">
-        <v>6850188</v>
+        <v>6850172</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121413976</v>
+        <v>121414636</v>
       </c>
       <c r="B15" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484940</v>
+        <v>484958</v>
       </c>
       <c r="R15" t="n">
-        <v>6850189</v>
+        <v>6850185</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121414725</v>
+        <v>121414555</v>
       </c>
       <c r="B16" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484937</v>
+        <v>484975</v>
       </c>
       <c r="R16" t="n">
-        <v>6850172</v>
+        <v>6850186</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2186,6 +2186,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2198,22 +2203,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121413920</v>
+        <v>121415337</v>
       </c>
       <c r="B17" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484950</v>
+        <v>485020</v>
       </c>
       <c r="R17" t="n">
-        <v>6850202</v>
+        <v>6850196</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121416640</v>
+        <v>121416560</v>
       </c>
       <c r="B18" t="n">
-        <v>56555</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,46 +2329,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Näveråsen, Näveråsen, Dlr</t>
+          <t>Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485045</v>
+        <v>485067</v>
       </c>
       <c r="R18" t="n">
-        <v>6850175</v>
+        <v>6850123</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2407,12 +2407,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 56788-2023 artfynd.xlsx
+++ b/artfynd/A 56788-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121413976</v>
+        <v>121414642</v>
       </c>
       <c r="B2" t="n">
         <v>98098</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484940</v>
+        <v>484941</v>
       </c>
       <c r="R2" t="n">
-        <v>6850189</v>
+        <v>6850185</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121413886</v>
+        <v>121413957</v>
       </c>
       <c r="B3" t="n">
         <v>98098</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484910</v>
+        <v>484948</v>
       </c>
       <c r="R3" t="n">
-        <v>6850188</v>
+        <v>6850191</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121413581</v>
+        <v>121413972</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484920</v>
+        <v>484943</v>
       </c>
       <c r="R4" t="n">
-        <v>6850189</v>
+        <v>6850255</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121416254</v>
+        <v>121415337</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485054</v>
+        <v>485020</v>
       </c>
       <c r="R5" t="n">
-        <v>6850120</v>
+        <v>6850196</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121413957</v>
+        <v>121413920</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484948</v>
+        <v>484950</v>
       </c>
       <c r="R6" t="n">
-        <v>6850191</v>
+        <v>6850202</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121413972</v>
+        <v>121414725</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484943</v>
+        <v>484937</v>
       </c>
       <c r="R7" t="n">
-        <v>6850255</v>
+        <v>6850172</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121413920</v>
+        <v>121416560</v>
       </c>
       <c r="B8" t="n">
         <v>98098</v>
@@ -1323,14 +1323,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näveråsen, Näveråsen, Dlr</t>
+          <t>Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484950</v>
+        <v>485067</v>
       </c>
       <c r="R8" t="n">
-        <v>6850202</v>
+        <v>6850123</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121414073</v>
+        <v>121414507</v>
       </c>
       <c r="B9" t="n">
         <v>98098</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484929</v>
+        <v>484938</v>
       </c>
       <c r="R9" t="n">
-        <v>6850187</v>
+        <v>6850191</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121416640</v>
+        <v>121414073</v>
       </c>
       <c r="B10" t="n">
-        <v>56558</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,46 +1503,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485045</v>
+        <v>484929</v>
       </c>
       <c r="R10" t="n">
-        <v>6850175</v>
+        <v>6850187</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,19 +1581,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121414593</v>
+        <v>121413581</v>
       </c>
       <c r="B11" t="n">
         <v>98098</v>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484949</v>
+        <v>484920</v>
       </c>
       <c r="R11" t="n">
-        <v>6850202</v>
+        <v>6850189</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121414507</v>
+        <v>121416254</v>
       </c>
       <c r="B12" t="n">
         <v>98098</v>
@@ -1740,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484938</v>
+        <v>485054</v>
       </c>
       <c r="R12" t="n">
-        <v>6850191</v>
+        <v>6850120</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121414642</v>
+        <v>121414636</v>
       </c>
       <c r="B13" t="n">
         <v>98098</v>
@@ -1842,7 +1837,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484941</v>
+        <v>484958</v>
       </c>
       <c r="R13" t="n">
         <v>6850185</v>
@@ -1892,19 +1887,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121414725</v>
+        <v>121414555</v>
       </c>
       <c r="B14" t="n">
         <v>98098</v>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484937</v>
+        <v>484975</v>
       </c>
       <c r="R14" t="n">
-        <v>6850172</v>
+        <v>6850186</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,6 +1977,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -1994,19 +1994,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121414636</v>
+        <v>121413976</v>
       </c>
       <c r="B15" t="n">
         <v>98098</v>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484958</v>
+        <v>484940</v>
       </c>
       <c r="R15" t="n">
-        <v>6850185</v>
+        <v>6850189</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121414555</v>
+        <v>121416640</v>
       </c>
       <c r="B16" t="n">
-        <v>98098</v>
+        <v>56558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,41 +2120,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484975</v>
+        <v>485045</v>
       </c>
       <c r="R16" t="n">
-        <v>6850186</v>
+        <v>6850175</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2184,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2203,19 +2203,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121415337</v>
+        <v>121413886</v>
       </c>
       <c r="B17" t="n">
         <v>98098</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485020</v>
+        <v>484910</v>
       </c>
       <c r="R17" t="n">
-        <v>6850196</v>
+        <v>6850188</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2305,19 +2305,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121416560</v>
+        <v>121414593</v>
       </c>
       <c r="B18" t="n">
         <v>98098</v>
@@ -2353,14 +2353,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Näveråsen, Dlr</t>
+          <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485067</v>
+        <v>484949</v>
       </c>
       <c r="R18" t="n">
-        <v>6850123</v>
+        <v>6850202</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2407,12 +2407,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 56788-2023 artfynd.xlsx
+++ b/artfynd/A 56788-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121414642</v>
+        <v>121414507</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484941</v>
+        <v>484938</v>
       </c>
       <c r="R2" t="n">
-        <v>6850185</v>
+        <v>6850191</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121413957</v>
+        <v>121414642</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484948</v>
+        <v>484941</v>
       </c>
       <c r="R3" t="n">
-        <v>6850191</v>
+        <v>6850185</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121413972</v>
+        <v>121413920</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484943</v>
+        <v>484950</v>
       </c>
       <c r="R4" t="n">
-        <v>6850255</v>
+        <v>6850202</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121415337</v>
+        <v>121413972</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485020</v>
+        <v>484943</v>
       </c>
       <c r="R5" t="n">
-        <v>6850196</v>
+        <v>6850255</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121413920</v>
+        <v>121414636</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484950</v>
+        <v>484958</v>
       </c>
       <c r="R6" t="n">
-        <v>6850202</v>
+        <v>6850185</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1188,7 +1188,7 @@
         <v>121414725</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121416560</v>
+        <v>121413976</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,17 +1323,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näveråsen, Dlr</t>
+          <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485067</v>
+        <v>484940</v>
       </c>
       <c r="R8" t="n">
-        <v>6850123</v>
+        <v>6850189</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121414507</v>
+        <v>121414073</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484938</v>
+        <v>484929</v>
       </c>
       <c r="R9" t="n">
-        <v>6850191</v>
+        <v>6850187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121414073</v>
+        <v>121415337</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484929</v>
+        <v>485020</v>
       </c>
       <c r="R10" t="n">
-        <v>6850187</v>
+        <v>6850196</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121413581</v>
+        <v>121416254</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484920</v>
+        <v>485054</v>
       </c>
       <c r="R11" t="n">
-        <v>6850189</v>
+        <v>6850120</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121416254</v>
+        <v>121414555</v>
       </c>
       <c r="B12" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485054</v>
+        <v>484975</v>
       </c>
       <c r="R12" t="n">
-        <v>6850120</v>
+        <v>6850186</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1773,6 +1773,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1785,22 +1790,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121414636</v>
+        <v>121416560</v>
       </c>
       <c r="B13" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,14 +1838,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Näveråsen, Näveråsen, Dlr</t>
+          <t>Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484958</v>
+        <v>485067</v>
       </c>
       <c r="R13" t="n">
-        <v>6850185</v>
+        <v>6850123</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121414555</v>
+        <v>121414593</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484975</v>
+        <v>484949</v>
       </c>
       <c r="R14" t="n">
-        <v>6850186</v>
+        <v>6850202</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1977,11 +1982,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -1994,22 +1994,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121413976</v>
+        <v>121416640</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>56559</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,41 +2018,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484940</v>
+        <v>485045</v>
       </c>
       <c r="R15" t="n">
-        <v>6850189</v>
+        <v>6850175</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2096,22 +2101,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121416640</v>
+        <v>121413581</v>
       </c>
       <c r="B16" t="n">
-        <v>56558</v>
+        <v>98104</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,46 +2125,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485045</v>
+        <v>484920</v>
       </c>
       <c r="R16" t="n">
-        <v>6850175</v>
+        <v>6850189</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>121413886</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121414593</v>
+        <v>121413957</v>
       </c>
       <c r="B18" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2357,13 +2357,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484949</v>
+        <v>484948</v>
       </c>
       <c r="R18" t="n">
-        <v>6850202</v>
+        <v>6850191</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2407,12 +2407,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 56788-2023 artfynd.xlsx
+++ b/artfynd/A 56788-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121414507</v>
+        <v>121414073</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484938</v>
+        <v>484929</v>
       </c>
       <c r="R2" t="n">
-        <v>6850191</v>
+        <v>6850187</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121414642</v>
+        <v>121414555</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484941</v>
+        <v>484975</v>
       </c>
       <c r="R3" t="n">
-        <v>6850185</v>
+        <v>6850186</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -855,6 +855,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121413920</v>
+        <v>121414725</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484950</v>
+        <v>484937</v>
       </c>
       <c r="R4" t="n">
-        <v>6850202</v>
+        <v>6850172</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121413972</v>
+        <v>121413957</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484943</v>
+        <v>484948</v>
       </c>
       <c r="R5" t="n">
-        <v>6850255</v>
+        <v>6850191</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121414636</v>
+        <v>121416640</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>56560</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1100,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484958</v>
+        <v>485045</v>
       </c>
       <c r="R6" t="n">
-        <v>6850185</v>
+        <v>6850175</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121414725</v>
+        <v>121413976</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484937</v>
+        <v>484940</v>
       </c>
       <c r="R7" t="n">
-        <v>6850172</v>
+        <v>6850189</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121413976</v>
+        <v>121415337</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484940</v>
+        <v>485020</v>
       </c>
       <c r="R8" t="n">
-        <v>6850189</v>
+        <v>6850196</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121414073</v>
+        <v>121413581</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,13 +1439,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484929</v>
+        <v>484920</v>
       </c>
       <c r="R9" t="n">
-        <v>6850187</v>
+        <v>6850189</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1489,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121415337</v>
+        <v>121413972</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485020</v>
+        <v>484943</v>
       </c>
       <c r="R10" t="n">
-        <v>6850196</v>
+        <v>6850255</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1581,22 +1591,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121416254</v>
+        <v>121414642</v>
       </c>
       <c r="B11" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485054</v>
+        <v>484941</v>
       </c>
       <c r="R11" t="n">
-        <v>6850120</v>
+        <v>6850185</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121414555</v>
+        <v>121416254</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484975</v>
+        <v>485054</v>
       </c>
       <c r="R12" t="n">
-        <v>6850186</v>
+        <v>6850120</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1773,11 +1783,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1790,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121416560</v>
+        <v>121414507</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,17 +1843,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Näveråsen, Dlr</t>
+          <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485067</v>
+        <v>484938</v>
       </c>
       <c r="R13" t="n">
-        <v>6850123</v>
+        <v>6850191</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,22 +1897,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121414593</v>
+        <v>121416560</v>
       </c>
       <c r="B14" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,14 +1945,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Näveråsen, Näveråsen, Dlr</t>
+          <t>Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484949</v>
+        <v>485067</v>
       </c>
       <c r="R14" t="n">
-        <v>6850202</v>
+        <v>6850123</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1994,22 +1999,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121416640</v>
+        <v>121413886</v>
       </c>
       <c r="B15" t="n">
-        <v>56559</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,46 +2023,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485045</v>
+        <v>484910</v>
       </c>
       <c r="R15" t="n">
-        <v>6850175</v>
+        <v>6850188</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121413581</v>
+        <v>121414593</v>
       </c>
       <c r="B16" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484920</v>
+        <v>484949</v>
       </c>
       <c r="R16" t="n">
-        <v>6850189</v>
+        <v>6850202</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121413886</v>
+        <v>121413920</v>
       </c>
       <c r="B17" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484910</v>
+        <v>484950</v>
       </c>
       <c r="R17" t="n">
-        <v>6850188</v>
+        <v>6850202</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2305,22 +2305,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121413957</v>
+        <v>121414636</v>
       </c>
       <c r="B18" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2357,13 +2357,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484948</v>
+        <v>484958</v>
       </c>
       <c r="R18" t="n">
-        <v>6850191</v>
+        <v>6850185</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 56788-2023 artfynd.xlsx
+++ b/artfynd/A 56788-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121414073</v>
+        <v>121416560</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näveråsen, Näveråsen, Dlr</t>
+          <t>Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484929</v>
+        <v>485067</v>
       </c>
       <c r="R2" t="n">
-        <v>6850187</v>
+        <v>6850123</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121414555</v>
+        <v>121413957</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484975</v>
+        <v>484948</v>
       </c>
       <c r="R3" t="n">
-        <v>6850186</v>
+        <v>6850191</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121414725</v>
+        <v>121414642</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484937</v>
+        <v>484941</v>
       </c>
       <c r="R4" t="n">
-        <v>6850172</v>
+        <v>6850185</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121413957</v>
+        <v>121414507</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1026,7 +1021,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484948</v>
+        <v>484938</v>
       </c>
       <c r="R5" t="n">
         <v>6850191</v>
@@ -1076,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121416640</v>
+        <v>121414073</v>
       </c>
       <c r="B6" t="n">
-        <v>56560</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,46 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485045</v>
+        <v>484929</v>
       </c>
       <c r="R6" t="n">
-        <v>6850175</v>
+        <v>6850187</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,19 +1173,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121413976</v>
+        <v>121414555</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1235,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484940</v>
+        <v>484975</v>
       </c>
       <c r="R7" t="n">
-        <v>6850189</v>
+        <v>6850186</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1271,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121415337</v>
+        <v>121416640</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>56560</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,41 +1304,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485020</v>
+        <v>485045</v>
       </c>
       <c r="R8" t="n">
-        <v>6850196</v>
+        <v>6850175</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,12 +1387,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121413972</v>
+        <v>121414725</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484943</v>
+        <v>484937</v>
       </c>
       <c r="R10" t="n">
-        <v>6850255</v>
+        <v>6850172</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121414642</v>
+        <v>121413920</v>
       </c>
       <c r="B11" t="n">
         <v>98105</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484941</v>
+        <v>484950</v>
       </c>
       <c r="R11" t="n">
-        <v>6850185</v>
+        <v>6850202</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1693,19 +1693,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121416254</v>
+        <v>121414593</v>
       </c>
       <c r="B12" t="n">
         <v>98105</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485054</v>
+        <v>484949</v>
       </c>
       <c r="R12" t="n">
-        <v>6850120</v>
+        <v>6850202</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121414507</v>
+        <v>121413976</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484938</v>
+        <v>484940</v>
       </c>
       <c r="R13" t="n">
-        <v>6850191</v>
+        <v>6850189</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,19 +1897,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121416560</v>
+        <v>121413886</v>
       </c>
       <c r="B14" t="n">
         <v>98105</v>
@@ -1945,14 +1945,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Näveråsen, Dlr</t>
+          <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485067</v>
+        <v>484910</v>
       </c>
       <c r="R14" t="n">
-        <v>6850123</v>
+        <v>6850188</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1999,19 +1999,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121413886</v>
+        <v>121415337</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484910</v>
+        <v>485020</v>
       </c>
       <c r="R15" t="n">
-        <v>6850188</v>
+        <v>6850196</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2101,19 +2101,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121414593</v>
+        <v>121416254</v>
       </c>
       <c r="B16" t="n">
         <v>98105</v>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484949</v>
+        <v>485054</v>
       </c>
       <c r="R16" t="n">
-        <v>6850202</v>
+        <v>6850120</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121413920</v>
+        <v>121413972</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484950</v>
+        <v>484943</v>
       </c>
       <c r="R17" t="n">
-        <v>6850202</v>
+        <v>6850255</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2305,12 +2305,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 56788-2023 artfynd.xlsx
+++ b/artfynd/A 56788-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121416560</v>
+        <v>121414507</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näveråsen, Dlr</t>
+          <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485067</v>
+        <v>484938</v>
       </c>
       <c r="R2" t="n">
-        <v>6850123</v>
+        <v>6850191</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121413957</v>
+        <v>121414555</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484948</v>
+        <v>484975</v>
       </c>
       <c r="R3" t="n">
-        <v>6850191</v>
+        <v>6850186</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121414642</v>
+        <v>121414725</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484941</v>
+        <v>484937</v>
       </c>
       <c r="R4" t="n">
-        <v>6850185</v>
+        <v>6850172</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121414507</v>
+        <v>121416640</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>56560</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +998,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484938</v>
+        <v>485045</v>
       </c>
       <c r="R5" t="n">
-        <v>6850191</v>
+        <v>6850175</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121414073</v>
+        <v>121416560</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1119,17 +1129,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Näveråsen, Näveråsen, Dlr</t>
+          <t>Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484929</v>
+        <v>485067</v>
       </c>
       <c r="R6" t="n">
-        <v>6850187</v>
+        <v>6850123</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121414555</v>
+        <v>121413957</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1225,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484975</v>
+        <v>484948</v>
       </c>
       <c r="R7" t="n">
-        <v>6850186</v>
+        <v>6850191</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121416640</v>
+        <v>121413972</v>
       </c>
       <c r="B8" t="n">
-        <v>56560</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,42 +1313,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485045</v>
+        <v>484943</v>
       </c>
       <c r="R8" t="n">
-        <v>6850175</v>
+        <v>6850255</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121413581</v>
+        <v>121414593</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484920</v>
+        <v>484949</v>
       </c>
       <c r="R9" t="n">
-        <v>6850189</v>
+        <v>6850202</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121414725</v>
+        <v>121414636</v>
       </c>
       <c r="B10" t="n">
         <v>98105</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484937</v>
+        <v>484958</v>
       </c>
       <c r="R10" t="n">
-        <v>6850172</v>
+        <v>6850185</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1591,19 +1591,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121413920</v>
+        <v>121413886</v>
       </c>
       <c r="B11" t="n">
         <v>98105</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484950</v>
+        <v>484910</v>
       </c>
       <c r="R11" t="n">
-        <v>6850202</v>
+        <v>6850188</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1693,19 +1693,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121414593</v>
+        <v>121413976</v>
       </c>
       <c r="B12" t="n">
         <v>98105</v>
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484949</v>
+        <v>484940</v>
       </c>
       <c r="R12" t="n">
-        <v>6850202</v>
+        <v>6850189</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,19 +1795,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121413976</v>
+        <v>121414073</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484940</v>
+        <v>484929</v>
       </c>
       <c r="R13" t="n">
-        <v>6850189</v>
+        <v>6850187</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121413886</v>
+        <v>121416254</v>
       </c>
       <c r="B14" t="n">
         <v>98105</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484910</v>
+        <v>485054</v>
       </c>
       <c r="R14" t="n">
-        <v>6850188</v>
+        <v>6850120</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121415337</v>
+        <v>121414642</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485020</v>
+        <v>484941</v>
       </c>
       <c r="R15" t="n">
-        <v>6850196</v>
+        <v>6850185</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2101,19 +2101,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121416254</v>
+        <v>121415337</v>
       </c>
       <c r="B16" t="n">
         <v>98105</v>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485054</v>
+        <v>485020</v>
       </c>
       <c r="R16" t="n">
-        <v>6850120</v>
+        <v>6850196</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2203,22 +2203,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121413972</v>
+        <v>121413581</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484943</v>
+        <v>484920</v>
       </c>
       <c r="R17" t="n">
-        <v>6850255</v>
+        <v>6850189</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121414636</v>
+        <v>121413920</v>
       </c>
       <c r="B18" t="n">
         <v>98105</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484958</v>
+        <v>484950</v>
       </c>
       <c r="R18" t="n">
-        <v>6850185</v>
+        <v>6850202</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 56788-2023 artfynd.xlsx
+++ b/artfynd/A 56788-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121414507</v>
+        <v>121413581</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484938</v>
+        <v>484920</v>
       </c>
       <c r="R2" t="n">
-        <v>6850191</v>
+        <v>6850189</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121414555</v>
+        <v>121413920</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484975</v>
+        <v>484950</v>
       </c>
       <c r="R3" t="n">
-        <v>6850186</v>
+        <v>6850202</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121414725</v>
+        <v>121413886</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484937</v>
+        <v>484910</v>
       </c>
       <c r="R4" t="n">
-        <v>6850172</v>
+        <v>6850188</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121416640</v>
+        <v>121414073</v>
       </c>
       <c r="B5" t="n">
-        <v>56560</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,46 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485045</v>
+        <v>484929</v>
       </c>
       <c r="R5" t="n">
-        <v>6850175</v>
+        <v>6850187</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121416560</v>
+        <v>121414507</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1129,17 +1119,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Näveråsen, Dlr</t>
+          <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485067</v>
+        <v>484938</v>
       </c>
       <c r="R6" t="n">
-        <v>6850123</v>
+        <v>6850191</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,12 +1173,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121413972</v>
+        <v>121414642</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484943</v>
+        <v>484941</v>
       </c>
       <c r="R8" t="n">
-        <v>6850255</v>
+        <v>6850185</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121414593</v>
+        <v>121416640</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>56560</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,41 +1401,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484949</v>
+        <v>485045</v>
       </c>
       <c r="R9" t="n">
-        <v>6850202</v>
+        <v>6850175</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121414636</v>
+        <v>121416254</v>
       </c>
       <c r="B10" t="n">
         <v>98105</v>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484958</v>
+        <v>485054</v>
       </c>
       <c r="R10" t="n">
-        <v>6850185</v>
+        <v>6850120</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1591,19 +1586,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121413886</v>
+        <v>121414593</v>
       </c>
       <c r="B11" t="n">
         <v>98105</v>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484910</v>
+        <v>484949</v>
       </c>
       <c r="R11" t="n">
-        <v>6850188</v>
+        <v>6850202</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1705,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121413976</v>
+        <v>121414555</v>
       </c>
       <c r="B12" t="n">
         <v>98105</v>
@@ -1745,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484940</v>
+        <v>484975</v>
       </c>
       <c r="R12" t="n">
-        <v>6850189</v>
+        <v>6850186</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1781,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121414073</v>
+        <v>121414725</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1847,13 +1847,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484929</v>
+        <v>484937</v>
       </c>
       <c r="R13" t="n">
-        <v>6850187</v>
+        <v>6850172</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,19 +1897,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121416254</v>
+        <v>121413976</v>
       </c>
       <c r="B14" t="n">
         <v>98105</v>
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485054</v>
+        <v>484940</v>
       </c>
       <c r="R14" t="n">
-        <v>6850120</v>
+        <v>6850189</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1999,19 +1999,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121414642</v>
+        <v>121415337</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484941</v>
+        <v>485020</v>
       </c>
       <c r="R15" t="n">
-        <v>6850185</v>
+        <v>6850196</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2101,19 +2101,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121415337</v>
+        <v>121414636</v>
       </c>
       <c r="B16" t="n">
         <v>98105</v>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485020</v>
+        <v>484958</v>
       </c>
       <c r="R16" t="n">
-        <v>6850196</v>
+        <v>6850185</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121413581</v>
+        <v>121416560</v>
       </c>
       <c r="B17" t="n">
         <v>98105</v>
@@ -2251,14 +2251,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näveråsen, Näveråsen, Dlr</t>
+          <t>Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484920</v>
+        <v>485067</v>
       </c>
       <c r="R17" t="n">
-        <v>6850189</v>
+        <v>6850123</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2305,22 +2305,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121413920</v>
+        <v>121413972</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484950</v>
+        <v>484943</v>
       </c>
       <c r="R18" t="n">
-        <v>6850202</v>
+        <v>6850255</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2407,12 +2407,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 56788-2023 artfynd.xlsx
+++ b/artfynd/A 56788-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121413581</v>
+        <v>121415337</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484920</v>
+        <v>485020</v>
       </c>
       <c r="R2" t="n">
-        <v>6850189</v>
+        <v>6850196</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121413920</v>
+        <v>121416560</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näveråsen, Näveråsen, Dlr</t>
+          <t>Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484950</v>
+        <v>485067</v>
       </c>
       <c r="R3" t="n">
-        <v>6850202</v>
+        <v>6850123</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121413886</v>
+        <v>121413920</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484910</v>
+        <v>484950</v>
       </c>
       <c r="R4" t="n">
-        <v>6850188</v>
+        <v>6850202</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121414073</v>
+        <v>121414507</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484929</v>
+        <v>484938</v>
       </c>
       <c r="R5" t="n">
-        <v>6850187</v>
+        <v>6850191</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121414507</v>
+        <v>121413957</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484938</v>
+        <v>484948</v>
       </c>
       <c r="R6" t="n">
         <v>6850191</v>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121413957</v>
+        <v>121416640</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>56561</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,41 +1197,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484948</v>
+        <v>485045</v>
       </c>
       <c r="R7" t="n">
-        <v>6850191</v>
+        <v>6850175</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121414642</v>
+        <v>121413972</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484941</v>
+        <v>484943</v>
       </c>
       <c r="R8" t="n">
-        <v>6850185</v>
+        <v>6850255</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121416640</v>
+        <v>121414593</v>
       </c>
       <c r="B9" t="n">
-        <v>56560</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,46 +1406,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485045</v>
+        <v>484949</v>
       </c>
       <c r="R9" t="n">
-        <v>6850175</v>
+        <v>6850202</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121416254</v>
+        <v>121414555</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485054</v>
+        <v>484975</v>
       </c>
       <c r="R10" t="n">
-        <v>6850120</v>
+        <v>6850186</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1574,6 +1574,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1586,22 +1591,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121414593</v>
+        <v>121414725</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484949</v>
+        <v>484937</v>
       </c>
       <c r="R11" t="n">
-        <v>6850202</v>
+        <v>6850172</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121414555</v>
+        <v>121414642</v>
       </c>
       <c r="B12" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484975</v>
+        <v>484941</v>
       </c>
       <c r="R12" t="n">
-        <v>6850186</v>
+        <v>6850185</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,11 +1783,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1795,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121414725</v>
+        <v>121416254</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484937</v>
+        <v>485054</v>
       </c>
       <c r="R13" t="n">
-        <v>6850172</v>
+        <v>6850120</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121413976</v>
+        <v>121414073</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484940</v>
+        <v>484929</v>
       </c>
       <c r="R14" t="n">
-        <v>6850189</v>
+        <v>6850187</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121415337</v>
+        <v>121413886</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485020</v>
+        <v>484910</v>
       </c>
       <c r="R15" t="n">
-        <v>6850196</v>
+        <v>6850188</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2101,22 +2101,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121414636</v>
+        <v>121413976</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484958</v>
+        <v>484940</v>
       </c>
       <c r="R16" t="n">
-        <v>6850185</v>
+        <v>6850189</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121416560</v>
+        <v>121413581</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,14 +2251,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näveråsen, Dlr</t>
+          <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485067</v>
+        <v>484920</v>
       </c>
       <c r="R17" t="n">
-        <v>6850123</v>
+        <v>6850189</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2305,22 +2305,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121413972</v>
+        <v>121414636</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484943</v>
+        <v>484958</v>
       </c>
       <c r="R18" t="n">
-        <v>6850255</v>
+        <v>6850185</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2407,12 +2407,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
